--- a/data/environmental/daily-measurements.xlsx
+++ b/data/environmental/daily-measurements.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashuffmyer/MyProjects/oysters/polyIC-larvae/data/environmental/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{955A0B8D-C4F7-6940-9BC9-12FB69F7C3A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F62CC90B-5EEA-3145-AA71-C7E70CAFB351}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30820" yWindow="-1460" windowWidth="18760" windowHeight="18760" xr2:uid="{00BD5C40-37F4-2C4B-83C9-57CC1D291904}"/>
+    <workbookView xWindow="12640" yWindow="760" windowWidth="17600" windowHeight="17760" xr2:uid="{00BD5C40-37F4-2C4B-83C9-57CC1D291904}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="36">
   <si>
     <t>PolyIC-tank1</t>
   </si>
@@ -126,6 +126,24 @@
   </si>
   <si>
     <t>group</t>
+  </si>
+  <si>
+    <t>low range</t>
+  </si>
+  <si>
+    <t>high range</t>
+  </si>
+  <si>
+    <t>mean temp</t>
+  </si>
+  <si>
+    <t>std error temp</t>
+  </si>
+  <si>
+    <t>mean pH</t>
+  </si>
+  <si>
+    <t>st error pH</t>
   </si>
 </sst>
 </file>
@@ -499,13 +517,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE0830F2-F0D8-2646-A72E-53EF0BB26B7B}">
-  <dimension ref="A1:I85"/>
+  <dimension ref="A1:N85"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.33203125" customWidth="1"/>
+    <col min="11" max="11" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>7</v>
       </c>
@@ -534,7 +553,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -563,7 +582,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -592,7 +611,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -621,7 +640,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -649,8 +668,20 @@
       <c r="I5" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K5" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" t="s">
+        <v>33</v>
+      </c>
+      <c r="M5" t="s">
+        <v>30</v>
+      </c>
+      <c r="N5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -678,8 +709,27 @@
       <c r="I6" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J6" t="s">
+        <v>14</v>
+      </c>
+      <c r="K6">
+        <f>AVERAGE(D2,D4,D6,D8,D10,D12)</f>
+        <v>24.899999999999995</v>
+      </c>
+      <c r="L6">
+        <f>STDEV(D2,D4,D6,D8,D10,D12)/SQRT(6)</f>
+        <v>0.78655366420014006</v>
+      </c>
+      <c r="M6">
+        <f>K6-L6</f>
+        <v>24.113446335799853</v>
+      </c>
+      <c r="N6">
+        <f>K6+L6</f>
+        <v>25.686553664200137</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -707,8 +757,27 @@
       <c r="I7" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K7">
+        <f>AVERAGE(D3,D5,D7,D9,D11,D13)</f>
+        <v>25.583333333333332</v>
+      </c>
+      <c r="L7">
+        <f>STDEV(D3,D5,D7,D9,D11,D13)/SQRT(6)</f>
+        <v>0.80017359227718676</v>
+      </c>
+      <c r="M7">
+        <f>K7-L7</f>
+        <v>24.783159741056146</v>
+      </c>
+      <c r="N7">
+        <f>K7+L7</f>
+        <v>26.383506925610519</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -737,7 +806,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -765,8 +834,20 @@
       <c r="I9" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K9" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" t="s">
+        <v>35</v>
+      </c>
+      <c r="M9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -794,8 +875,27 @@
       <c r="I10" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J10" t="s">
+        <v>14</v>
+      </c>
+      <c r="K10">
+        <f>AVERAGE(E2,E4,E8,E10,E12)</f>
+        <v>8.2579999999999991</v>
+      </c>
+      <c r="L10">
+        <f>STDEV(E2,E4,E8,E10,E12)/SQRT(5)</f>
+        <v>5.342284155677228E-2</v>
+      </c>
+      <c r="M10">
+        <f>K10-L10</f>
+        <v>8.204577158443227</v>
+      </c>
+      <c r="N10">
+        <f>K10+L10</f>
+        <v>8.3114228415567712</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -823,8 +923,27 @@
       <c r="I11" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J11" t="s">
+        <v>17</v>
+      </c>
+      <c r="K11">
+        <f>AVERAGE(E3,E5,E9,E11,E13)</f>
+        <v>8.2540000000000013</v>
+      </c>
+      <c r="L11">
+        <f>STDEV(E3,E5,E9,E11,E13)/SQRT(5)</f>
+        <v>6.0299253726725295E-2</v>
+      </c>
+      <c r="M11">
+        <f>K11-L11</f>
+        <v>8.1937007462732758</v>
+      </c>
+      <c r="N11">
+        <f>K11+L11</f>
+        <v>8.3142992537267268</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -853,7 +972,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -882,7 +1001,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -911,7 +1030,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -940,7 +1059,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>20</v>
       </c>
